--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486422_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486422_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6132</v>
+        <v>1.6453</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9342</v>
+        <v>2.0279</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.321</v>
+        <v>-0.3827</v>
       </c>
       <c r="G2" t="n">
         <v>-0.8639</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7621</v>
+        <v>-0.73</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4759</v>
+        <v>-0.3821</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2863</v>
+        <v>-0.3479</v>
       </c>
       <c r="V2" t="n">
         <v>2.8042</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. GIOVANNETTI</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5154</v>
+        <v>0.2027</v>
       </c>
       <c r="E3" t="n">
-        <v>2.325</v>
+        <v>-0.0502</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8096</v>
+        <v>0.2529</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.7813</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0794</v>
+        <v>0.3163</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.8607</v>
+        <v>-0.3825</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2494</v>
+        <v>0.0182</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8797</v>
+        <v>0.0182</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6303</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.0307</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8003</v>
+        <v>0.298</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.2304</v>
+        <v>-0.3825</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7401</v>
+        <v>0.435</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6887</v>
+        <v>-0.1661</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2077</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.519</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. SOLA IDRISU</t>
+          <t>L. GIOVANNETTI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1033</v>
+        <v>-0.0324</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1187</v>
+        <v>1.4381</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2221</v>
+        <v>-1.4706</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-1.7813</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3163</v>
+        <v>1.0794</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3825</v>
+        <v>-2.8607</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0182</v>
+        <v>1.2494</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0182</v>
+        <v>1.8797</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.6303</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-3.0307</v>
       </c>
       <c r="N4" t="n">
-        <v>0.298</v>
+        <v>-0.8003</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3825</v>
+        <v>-2.2304</v>
       </c>
       <c r="P4" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>0.435</v>
+        <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2655</v>
+        <v>0.1409</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.137</v>
+        <v>0.3209</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1285</v>
+        <v>-0.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7638</v>
+        <v>-0.2903</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5258</v>
+        <v>2.0918</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.2896</v>
+        <v>-2.3821</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5107</v>
@@ -844,13 +844,13 @@
         <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4282</v>
+        <v>0.0454</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.822</v>
+        <v>-0.256</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3938</v>
+        <v>0.3013</v>
       </c>
       <c r="V5" t="n">
         <v>-1.13</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8865</v>
+        <v>-0.9768</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6478</v>
+        <v>-1.399</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7613</v>
+        <v>0.4223</v>
       </c>
       <c r="G6" t="n">
         <v>-0.8260999999999999</v>
@@ -922,13 +922,13 @@
         <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3099</v>
+        <v>0.2196</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.411</v>
+        <v>-0.1622</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7209</v>
+        <v>0.3818</v>
       </c>
       <c r="V6" t="n">
         <v>0.9347</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0092</v>
+        <v>-1.7056</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9325</v>
+        <v>-0.7523</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0767</v>
+        <v>-0.9534</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3024</v>
@@ -1000,13 +1000,13 @@
         <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4898</v>
+        <v>-0.1863</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3425</v>
+        <v>-0.1622</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1473</v>
+        <v>-0.024</v>
       </c>
       <c r="V7" t="n">
         <v>-1.8695</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1248</v>
+        <v>-1.778</v>
       </c>
       <c r="E8" t="n">
-        <v>0.13</v>
+        <v>0.3535</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2548</v>
+        <v>-2.1315</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2837</v>
@@ -1078,13 +1078,13 @@
         <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9933</v>
+        <v>-0.6465</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8099</v>
+        <v>-0.5864</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1834</v>
+        <v>-0.0601</v>
       </c>
       <c r="V8" t="n">
         <v>0.3698</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.006</v>
+        <v>-2.4104</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9129</v>
+        <v>-0.4407</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.093</v>
+        <v>-1.9698</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6321</v>
@@ -1156,13 +1156,13 @@
         <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1988</v>
+        <v>-0.6032</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9469</v>
+        <v>-0.4747</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2519</v>
+        <v>-0.1286</v>
       </c>
       <c r="V9" t="n">
         <v>1.13</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9104</v>
+        <v>-3.3089</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3965</v>
+        <v>-2.0107</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5139</v>
+        <v>-1.2982</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0783</v>
@@ -1234,13 +1234,13 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.1006</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6165</v>
+        <v>-0.2307</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0857</v>
+        <v>0.1301</v>
       </c>
       <c r="V10" t="n">
         <v>-1.13</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8074</v>
+        <v>-5.1589</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5289</v>
+        <v>-3.5722</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2785</v>
+        <v>-1.5867</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7008</v>
@@ -1312,13 +1312,13 @@
         <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.149</v>
+        <v>-0.5004999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3389</v>
+        <v>-0.3821</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1899</v>
+        <v>-0.1184</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.8706</v>
+        <v>-6.6209</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0176</v>
+        <v>-3.6139</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.853</v>
+        <v>-3.0071</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9717</v>
@@ -1390,13 +1390,13 @@
         <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9848</v>
+        <v>-0.7351</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0839</v>
+        <v>-0.6801</v>
       </c>
       <c r="U12" t="n">
-        <v>0.09909999999999999</v>
+        <v>-0.055</v>
       </c>
       <c r="V12" t="n">
         <v>-2.044</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-22.1468</v>
+        <v>-20.4342</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.639900000000001</v>
+        <v>-5.9277</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.5067</v>
+        <v>-14.5069</v>
       </c>
       <c r="G13" t="n">
         <v>-15.0172</v>
       </c>
       <c r="H13" t="n">
-        <v>1.473599999999999</v>
+        <v>1.4736</v>
       </c>
       <c r="I13" t="n">
         <v>-16.4909</v>
@@ -1447,7 +1447,7 @@
         <v>10.464</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.661300000000002</v>
+        <v>-5.6613</v>
       </c>
       <c r="M13" t="n">
         <v>-19.82</v>
@@ -1468,10 +1468,10 @@
         <v>11.9626</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.975</v>
+        <v>-3.2624</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.7768</v>
+        <v>-3.0641</v>
       </c>
       <c r="U13" t="n">
         <v>-0.1984</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.8011</v>
+        <v>8.9206</v>
       </c>
       <c r="E14" t="n">
-        <v>6.8001</v>
+        <v>7.1353</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0011</v>
+        <v>1.7853</v>
       </c>
       <c r="G14" t="n">
         <v>7.104</v>
@@ -1546,13 +1546,13 @@
         <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0429</v>
+        <v>0.0766</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.4182</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7106</v>
+        <v>0.4948</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. VUCETIC</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.7893</v>
+        <v>8.168200000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>7.5335</v>
+        <v>6.4407</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2558</v>
+        <v>1.7275</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3624</v>
+        <v>4.9626</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0005</v>
+        <v>1.8979</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3619</v>
+        <v>3.0647</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3841</v>
+        <v>5.4378</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8979</v>
+        <v>3.5253</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4862</v>
+        <v>1.9125</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0217</v>
+        <v>-0.4751</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8974</v>
+        <v>-1.6274</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1243</v>
+        <v>1.1522</v>
       </c>
       <c r="P15" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>0.87</v>
+        <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6221</v>
+        <v>0.7706</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8242</v>
+        <v>-0.1694</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9347</v>
+        <v>1.13</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3252</v>
+        <v>2.2599</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3904</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>V. VUCETIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.7263</v>
+        <v>6.8207</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9937</v>
+        <v>6.4159</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7326</v>
+        <v>0.4048</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9626</v>
+        <v>3.3624</v>
       </c>
       <c r="H16" t="n">
+        <v>1.0005</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.3619</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.3841</v>
+      </c>
+      <c r="K16" t="n">
         <v>1.8979</v>
       </c>
-      <c r="I16" t="n">
-        <v>3.0647</v>
-      </c>
-      <c r="J16" t="n">
-        <v>5.4378</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.5253</v>
-      </c>
       <c r="L16" t="n">
-        <v>1.9125</v>
+        <v>2.4862</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4751</v>
+        <v>-1.0217</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6274</v>
+        <v>-0.8974</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1522</v>
+        <v>-0.1243</v>
       </c>
       <c r="P16" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3926</v>
+        <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3287</v>
+        <v>1.6535</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6165</v>
+        <v>0.7066</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.9469</v>
       </c>
       <c r="V16" t="n">
-        <v>1.13</v>
+        <v>0.9347</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2599</v>
+        <v>1.3252</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.636</v>
+        <v>5.7464</v>
       </c>
       <c r="E17" t="n">
-        <v>4.3754</v>
+        <v>4.1519</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2605</v>
+        <v>1.5945</v>
       </c>
       <c r="G17" t="n">
         <v>1.8862</v>
@@ -1780,13 +1780,13 @@
         <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4898</v>
+        <v>0.6002</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1971</v>
+        <v>-0.0264</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2927</v>
+        <v>0.6267</v>
       </c>
       <c r="V17" t="n">
         <v>2.8249</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.0593</v>
+        <v>3.4434</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2671</v>
+        <v>2.3789</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7922</v>
+        <v>1.0645</v>
       </c>
       <c r="G18" t="n">
         <v>2.2561</v>
@@ -1858,13 +1858,13 @@
         <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5857</v>
+        <v>0.9698</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1971</v>
+        <v>0.3088</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3886</v>
+        <v>0.6609</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. LEVY</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0344</v>
+        <v>2.0529</v>
       </c>
       <c r="E19" t="n">
-        <v>1.504</v>
+        <v>0.9243</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5304</v>
+        <v>1.1287</v>
       </c>
       <c r="G19" t="n">
-        <v>0.829</v>
+        <v>1.479</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4927</v>
+        <v>0.1339</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3363</v>
+        <v>1.3451</v>
       </c>
       <c r="J19" t="n">
-        <v>0.896</v>
+        <v>1.8027</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8577</v>
+        <v>1.2473</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0382</v>
+        <v>0.5554</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.067</v>
+        <v>-0.3237</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.365</v>
+        <v>-1.1134</v>
       </c>
       <c r="O19" t="n">
-        <v>0.298</v>
+        <v>0.7897</v>
       </c>
       <c r="P19" t="n">
         <v>0.2175</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6388</v>
+        <v>0.9214</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6081</v>
+        <v>0.2091</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0308</v>
+        <v>0.7123</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3491</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3491</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>G. LEVY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8557</v>
+        <v>1.5758</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0302</v>
+        <v>1.1688</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8255</v>
+        <v>0.4071</v>
       </c>
       <c r="G20" t="n">
-        <v>1.479</v>
+        <v>0.829</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1339</v>
+        <v>0.4927</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3451</v>
+        <v>0.3363</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8027</v>
+        <v>0.896</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2473</v>
+        <v>0.8577</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5554</v>
+        <v>0.0382</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3237</v>
+        <v>-0.067</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1134</v>
+        <v>-0.365</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7897</v>
+        <v>0.298</v>
       </c>
       <c r="P20" t="n">
         <v>0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2758</v>
+        <v>0.1803</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.2728</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4092</v>
+        <v>-0.0925</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.3491</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>M. RODRIGUEZ BARRIENTOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0781</v>
+        <v>-0.6655</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7393999999999999</v>
+        <v>0.5324</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3387</v>
+        <v>-1.1979</v>
       </c>
       <c r="G21" t="n">
-        <v>0.284</v>
+        <v>-0.3243</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7511</v>
+        <v>-1.3411</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0351</v>
+        <v>1.0168</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1558</v>
+        <v>0.6081</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0793</v>
+        <v>-0.5776</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0765</v>
+        <v>1.1857</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1282</v>
+        <v>-0.9324</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8304</v>
+        <v>-0.7635</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9586</v>
+        <v>-0.1689</v>
       </c>
       <c r="P21" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0071</v>
+        <v>0.0493</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7367</v>
+        <v>-0.0757</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2705</v>
+        <v>0.125</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.8042</v>
+        <v>-0.3904</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.5443</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.2599</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ BARRIENTOS</t>
+          <t>A. WINTERING</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1241</v>
+        <v>-1.8824</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1971</v>
+        <v>-3.58</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3212</v>
+        <v>1.6976</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3243</v>
+        <v>-1.9449</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3411</v>
+        <v>-1.7759</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0168</v>
+        <v>-0.1689</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6081</v>
+        <v>-2.305</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5776</v>
+        <v>-1.5599</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1857</v>
+        <v>-0.7451</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9324</v>
+        <v>0.3601</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7635</v>
+        <v>-0.216</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1689</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4093</v>
+        <v>0.28</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.411</v>
+        <v>-0.1875</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0017</v>
+        <v>0.4675</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. WINTERING</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8593</v>
+        <v>-1.9413</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8035</v>
+        <v>-1.6334</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9442</v>
+        <v>-0.3079</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9449</v>
+        <v>0.284</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.7759</v>
+        <v>-0.7511</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1689</v>
+        <v>1.0351</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.305</v>
+        <v>0.1558</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5599</v>
+        <v>0.0793</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7451</v>
+        <v>0.0765</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3601</v>
+        <v>0.1282</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.216</v>
+        <v>-0.8304</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.9586</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R23" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3031</v>
+        <v>0.1439</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.411</v>
+        <v>-0.1574</v>
       </c>
       <c r="U23" t="n">
-        <v>0.714</v>
+        <v>0.3013</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.8042</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.5443</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9384</v>
+        <v>-3.7457</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.865</v>
+        <v>-3.6414</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0735</v>
+        <v>-0.1043</v>
       </c>
       <c r="G24" t="n">
         <v>-0.3763</v>
@@ -2326,13 +2326,13 @@
         <v>0.435</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1696</v>
+        <v>0.0231</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.411</v>
+        <v>-0.1875</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2414</v>
+        <v>0.2106</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5649999999999999</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.7556</v>
+        <v>-5.6015</v>
       </c>
       <c r="E25" t="n">
         <v>-5.7866</v>
       </c>
       <c r="F25" t="n">
-        <v>0.031</v>
+        <v>0.1851</v>
       </c>
       <c r="G25" t="n">
         <v>-4.5006</v>
@@ -2404,13 +2404,13 @@
         <v>1.9576</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1027</v>
+        <v>0.0514</v>
       </c>
       <c r="T25" t="n">
         <v>-0.0769</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0258</v>
+        <v>0.1283</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9347</v>
@@ -2437,28 +2437,28 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>22.1466</v>
+        <v>22.8916</v>
       </c>
       <c r="E26" t="n">
-        <v>14.5066</v>
+        <v>14.50679999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>7.639899999999999</v>
+        <v>8.385</v>
       </c>
       <c r="G26" t="n">
         <v>15.0172</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.473800000000001</v>
+        <v>-1.4738</v>
       </c>
       <c r="I26" t="n">
         <v>16.491</v>
       </c>
       <c r="J26" t="n">
-        <v>19.8199</v>
+        <v>19.81989999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>8.990499999999999</v>
+        <v>8.990500000000001</v>
       </c>
       <c r="L26" t="n">
         <v>10.8292</v>
@@ -2470,10 +2470,10 @@
         <v>-10.4642</v>
       </c>
       <c r="O26" t="n">
-        <v>5.6615</v>
+        <v>5.661499999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>2.175</v>
+        <v>2.174999999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>-11.9627</v>
@@ -2482,13 +2482,13 @@
         <v>14.1378</v>
       </c>
       <c r="S26" t="n">
-        <v>4.975000000000001</v>
+        <v>5.720100000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1982999999999999</v>
+        <v>0.1983000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>4.776699999999999</v>
+        <v>5.521800000000002</v>
       </c>
       <c r="V26" t="n">
         <v>-0.02060000000000006</v>
@@ -2497,7 +2497,7 @@
         <v>6.4513</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.471999999999999</v>
+        <v>-6.472</v>
       </c>
     </row>
   </sheetData>
